--- a/data/BIG3_tracker.xlsx
+++ b/data/BIG3_tracker.xlsx
@@ -1018,7 +1018,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BIG3 週次トラッカー  （更新: 2026-09-06）</t>
+          <t>BIG3 週次トラッカー  （更新: 2026-09-13）</t>
         </is>
       </c>
     </row>

--- a/data/BIG3_tracker.xlsx
+++ b/data/BIG3_tracker.xlsx
@@ -1018,7 +1018,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BIG3 週次トラッカー  （更新: 2026-09-13）</t>
+          <t>BIG3 週次トラッカー  （更新: 2026-09-20）</t>
         </is>
       </c>
     </row>

--- a/data/BIG3_tracker.xlsx
+++ b/data/BIG3_tracker.xlsx
@@ -1018,7 +1018,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BIG3 週次トラッカー  （更新: 2026-09-20）</t>
+          <t>BIG3 週次トラッカー  （更新: 2026-09-28）</t>
         </is>
       </c>
     </row>

--- a/data/BIG3_tracker.xlsx
+++ b/data/BIG3_tracker.xlsx
@@ -1018,7 +1018,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BIG3 週次トラッカー  （更新: 2026-09-28）</t>
+          <t>BIG3 週次トラッカー  （更新: 2026-10-05）</t>
         </is>
       </c>
     </row>

--- a/data/BIG3_tracker.xlsx
+++ b/data/BIG3_tracker.xlsx
@@ -1018,7 +1018,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BIG3 週次トラッカー  （更新: 2026-10-05）</t>
+          <t>BIG3 週次トラッカー  （更新: 2026-10-12）</t>
         </is>
       </c>
     </row>

--- a/data/BIG3_tracker.xlsx
+++ b/data/BIG3_tracker.xlsx
@@ -1018,7 +1018,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BIG3 週次トラッカー  （更新: 2026-10-12）</t>
+          <t>BIG3 週次トラッカー  （更新: 2026-10-18）</t>
         </is>
       </c>
     </row>

--- a/data/BIG3_tracker.xlsx
+++ b/data/BIG3_tracker.xlsx
@@ -1018,7 +1018,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BIG3 週次トラッカー  （更新: 2026-10-18）</t>
+          <t>BIG3 週次トラッカー  （更新: 2026-10-25）</t>
         </is>
       </c>
     </row>
